--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,51 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2855,8 +2980,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2871,681 +3000,678 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쾌지나 칭칭 — 민요채보-3/쾌지나 칭칭.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">쾌지나 칭칭</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">며</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">잡</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">많</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="17"/>
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">쾌</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="19"/>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="19"/>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="19"/>
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="I4" s="19"/>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">많</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="E5" s="20"/>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">칭</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="17"/>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">잔</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="17"/>
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="17"/>
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="17"/>
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">칭</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="19"/>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">엔</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">칭</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="M7" s="19"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="20"/>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="C9" s="17"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="17"/>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="I9" s="17"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">칭</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="L10" s="14"/>
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="G11" s="20"/>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="20"/>
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="14"/>
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">빈</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M12" s="17"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="19"/>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="19"/>
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">姑
 며
 姑
-―
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 칭</t>
-        </is>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="20"/>
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
+      <c r="M14" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1604,322 +1633,322 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">쾌지나 칭칭</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
+      <c r="M3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M4" s="9"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I4" s="23"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="10"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="8"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="23"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="9"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="24"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="G8" s="24"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="24"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
+      <c r="M8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="8"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="9"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="10"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="8"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -1614,24 +1614,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -1875,7 +1875,7 @@
       <c r="L9" s="21"/>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -1890,7 +1890,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -1905,7 +1905,7 @@
       <c r="L11" s="21"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -1920,7 +1920,7 @@
       <c r="L12" s="21"/>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -1935,7 +1935,7 @@
       <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>

--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -222,6 +227,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1657,37 +1671,37 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="25"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="25"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
+      <c r="K3" s="25"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="25"/>
     </row>
     <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
@@ -1696,33 +1710,33 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="26"/>
       <c r="J4" s="21"/>
-      <c r="K4" s="23"/>
+      <c r="K4" s="26"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="23"/>
+      <c r="M4" s="26"/>
     </row>
     <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
@@ -1731,21 +1745,21 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E5" s="24"/>
+      <c r="E5" s="27"/>
       <c r="F5" s="21"/>
-      <c r="G5" s="24"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="21"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="27"/>
       <c r="J5" s="21"/>
-      <c r="K5" s="24"/>
+      <c r="K5" s="27"/>
       <c r="L5" s="21"/>
-      <c r="M5" s="24"/>
+      <c r="M5" s="27"/>
     </row>
     <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
@@ -1754,37 +1768,37 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="25"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K6" s="22"/>
+      <c r="K6" s="25"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="25"/>
     </row>
     <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
@@ -1793,33 +1807,33 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I7" s="23"/>
+      <c r="I7" s="26"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="26"/>
       <c r="L7" s="21"/>
-      <c r="M7" s="23"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
@@ -1828,127 +1842,127 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C8" s="24"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I8" s="24"/>
+      <c r="I8" s="27"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="27"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="M8" s="24"/>
+      <c r="M8" s="27"/>
     </row>
     <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="21"/>
-      <c r="G9" s="22"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="21"/>
-      <c r="I9" s="22"/>
+      <c r="I9" s="25"/>
       <c r="J9" s="21"/>
-      <c r="K9" s="22"/>
+      <c r="K9" s="25"/>
       <c r="L9" s="21"/>
-      <c r="M9" s="22"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="23"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="21"/>
-      <c r="E10" s="23"/>
+      <c r="E10" s="26"/>
       <c r="F10" s="21"/>
-      <c r="G10" s="23"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="21"/>
-      <c r="I10" s="23"/>
+      <c r="I10" s="26"/>
       <c r="J10" s="21"/>
-      <c r="K10" s="23"/>
+      <c r="K10" s="26"/>
       <c r="L10" s="21"/>
-      <c r="M10" s="23"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="24"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="21"/>
-      <c r="E11" s="24"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="21"/>
-      <c r="G11" s="24"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="21"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="21"/>
-      <c r="K11" s="24"/>
+      <c r="K11" s="27"/>
       <c r="L11" s="21"/>
-      <c r="M11" s="24"/>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="21"/>
-      <c r="I12" s="22"/>
+      <c r="I12" s="25"/>
       <c r="J12" s="21"/>
-      <c r="K12" s="22"/>
+      <c r="K12" s="25"/>
       <c r="L12" s="21"/>
-      <c r="M12" s="22"/>
+      <c r="M12" s="25"/>
     </row>
     <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="21"/>
-      <c r="E13" s="23"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="23"/>
+      <c r="I13" s="26"/>
       <c r="J13" s="21"/>
-      <c r="K13" s="23"/>
+      <c r="K13" s="26"/>
       <c r="L13" s="21"/>
-      <c r="M13" s="23"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="24"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="21"/>
-      <c r="E14" s="24"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="24"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="24"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="21"/>
-      <c r="K14" s="24"/>
+      <c r="K14" s="27"/>
       <c r="L14" s="21"/>
-      <c r="M14" s="24"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,19 +218,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -332,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
     </row>
@@ -344,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
     </row>
@@ -368,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
     </row>
@@ -378,7 +376,11 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 35%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -404,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12정간, 굿거리(3/4). 머리 "쾌지나 칭칭 굿거리". 율명·기호 위주 전사. 가사 칸(각 율명열 오른쪽)은 사용자가 채우도록 비워 둠. 글씨 흘림 심해 일부 칸 추정. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
@@ -590,18 +592,27 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲仲</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲仲</t>
-        </is>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="4"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|仲</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+仲</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쾌지</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위 仲 작게 덧씀(정정 표시?)</t>
+        </is>
+      </c>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -625,18 +636,26 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="4"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲 아래 물결선</t>
+        </is>
+      </c>
       <c r="K3" s="2"/>
     </row>
     <row r="4">
@@ -670,7 +689,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칭</t>
+        </is>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="2"/>
     </row>
@@ -697,15 +720,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칭</t>
+        </is>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
@@ -719,28 +746,32 @@
         </is>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="2"/>
     </row>
@@ -754,17 +785,17 @@
         </is>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2">
         <v>4</v>
       </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
@@ -775,7 +806,11 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
       <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
@@ -789,16 +824,16 @@
         </is>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -810,7 +845,11 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
@@ -824,29 +863,34 @@
         </is>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·|△</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·
+△</t>
+        </is>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 표시 ∂ 모양, △로 추정</t>
+        </is>
+      </c>
       <c r="K9" s="2"/>
     </row>
     <row r="10">
@@ -859,10 +903,10 @@
         </is>
       </c>
       <c r="C10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -870,18 +914,26 @@
       <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="4"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칭처럼도 보임</t>
+        </is>
+      </c>
       <c r="K10" s="2"/>
     </row>
     <row r="11">
@@ -894,10 +946,10 @@
         </is>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2">
         <v>2</v>
@@ -907,15 +959,19 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천</t>
+        </is>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
@@ -929,25 +985,25 @@
         </is>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -964,28 +1020,32 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
       <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
@@ -999,28 +1059,32 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2">
         <v>2</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늘</t>
+        </is>
+      </c>
       <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
@@ -1034,28 +1098,32 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엔</t>
+        </is>
+      </c>
       <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
@@ -1069,29 +1137,38 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|汰</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+汰</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 흘림(氵+갈고리)</t>
+        </is>
+      </c>
       <c r="K16" s="2"/>
     </row>
     <row r="17">
@@ -1104,28 +1181,32 @@
         </is>
       </c>
       <c r="C17" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="I17" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
+        </is>
+      </c>
       <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
@@ -1139,28 +1220,32 @@
         </is>
       </c>
       <c r="C18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1174,29 +1259,38 @@
         </is>
       </c>
       <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2">
         <v>4</v>
       </c>
-      <c r="D19" s="2">
-        <v>4</v>
-      </c>
-      <c r="E19" s="2">
-        <v>6</v>
-      </c>
-      <c r="F19" s="2">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="4"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">많</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 강처럼 보임</t>
+        </is>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1209,29 +1303,33 @@
         </is>
       </c>
       <c r="C20" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸에 ㅣ 표시</t>
+        </is>
+      </c>
       <c r="K20" s="2"/>
     </row>
     <row r="21">
@@ -1244,28 +1342,32 @@
         </is>
       </c>
       <c r="C21" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1279,28 +1381,32 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그</t>
+        </is>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
@@ -1314,25 +1420,25 @@
         </is>
       </c>
       <c r="C23" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1349,29 +1455,37 @@
         </is>
       </c>
       <c r="C24" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">녀</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 녀/뉘?</t>
+        </is>
+      </c>
       <c r="K24" s="2"/>
     </row>
     <row r="25">
@@ -1384,29 +1498,37 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2">
         <v>2</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="4"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 흘림(氵+갈고리)</t>
+        </is>
+      </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1419,25 +1541,25 @@
         </is>
       </c>
       <c r="C26" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I26" s="2"/>
@@ -1454,28 +1576,33 @@
         </is>
       </c>
       <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2">
         <v>6</v>
       </c>
-      <c r="D27" s="2">
-        <v>6</v>
-      </c>
-      <c r="E27" s="2">
-        <v>2</v>
-      </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢|汰</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I27" s="2"/>
+          <t xml:space="preserve">潢
+汰</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1489,28 +1616,32 @@
         </is>
       </c>
       <c r="C28" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잡</t>
+        </is>
+      </c>
       <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
@@ -1524,28 +1655,32 @@
         </is>
       </c>
       <c r="C29" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1559,29 +1694,38 @@
         </is>
       </c>
       <c r="C30" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 古처럼 흘림, 1절 가락과 같아 南</t>
+        </is>
+      </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1594,33 +1738,76 @@
         </is>
       </c>
       <c r="C31" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/쾌지나 칭칭.png</t>
+        </is>
+      </c>
+      <c r="C32" s="2">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">며</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 古처럼 흘림, 1절 가락과 같아 南</t>
+        </is>
+      </c>
+      <c r="K32" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K31"/>
+  <autoFilter ref="A1:K32"/>
 </worksheet>
 </file>
 
@@ -1634,18 +1821,12 @@
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="29.14" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1657,316 +1838,349 @@
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-    </row>
-    <row r="3" ht="29.14" customHeight="1">
+    </row>
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="25"/>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲仲</t>
-        </is>
-      </c>
-      <c r="M3" s="25"/>
-    </row>
-    <row r="4" ht="29.14" customHeight="1">
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+仲</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쾌
+지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">녀</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="28"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="26"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M4" s="26"/>
-    </row>
-    <row r="5" ht="29.14" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="27"/>
-    </row>
-    <row r="6" ht="29.14" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K6" s="25"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="25"/>
-    </row>
-    <row r="7" ht="29.14" customHeight="1">
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칭</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C7" s="26"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="26"/>
-    </row>
-    <row r="8" ht="29.14" customHeight="1">
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늘</t>
+        </is>
+      </c>
+      <c r="F7" s="21"/>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C8" s="27"/>
+          <t xml:space="preserve">潢
+汰</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無姑</t>
-        </is>
-      </c>
-      <c r="E8" s="27"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엔</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="G8" s="27"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I8" s="27"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="K8" s="27"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="M8" s="27"/>
-    </row>
-    <row r="9" ht="29.14" customHeight="1">
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칭</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="25"/>
-    </row>
-    <row r="10" ht="29.14" customHeight="1">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잡</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+汰</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="26"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
+        </is>
+      </c>
       <c r="F10" s="21"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="26"/>
-    </row>
-    <row r="11" ht="29.14" customHeight="1">
+      <c r="G10" s="25"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="F11" s="21"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="27"/>
-    </row>
-    <row r="12" ht="29.14" customHeight="1">
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="25"/>
-    </row>
-    <row r="13" ht="29.14" customHeight="1">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">많</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="21"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
       <c r="E13" s="26"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="26"/>
-    </row>
-    <row r="14" ht="29.14" customHeight="1">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="21"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">며</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
       <c r="G14" s="27"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">㴌|汰</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢 흘림(氵+갈고리)</t>
+          <t xml:space="preserve">㴌 흘림(氵+갈고리)</t>
         </is>
       </c>
       <c r="K16" s="2"/>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢 흘림(氵+갈고리)</t>
+          <t xml:space="preserve">㴌 흘림(氵+갈고리)</t>
         </is>
       </c>
       <c r="K25" s="2"/>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">㴌|汰</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
@@ -1928,7 +1928,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -1982,7 +1982,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>

--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -1810,6 +1810,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1820,10 +1823,10 @@
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="52.21" customHeight="1">
+    <row r="2" ht="43.01" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1836,7 +1839,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" ht="52.21" customHeight="1">
+    <row r="3" ht="63.87" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1871,7 +1874,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="52.21" customHeight="1">
+    <row r="4" ht="63.87" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1900,7 +1903,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52.21" customHeight="1">
+    <row r="5" ht="63.87" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -1921,7 +1924,7 @@
       <c r="F5" s="21"/>
       <c r="G5" s="28"/>
     </row>
-    <row r="6" ht="52.21" customHeight="1">
+    <row r="6" ht="63.87" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -1954,7 +1957,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52.21" customHeight="1">
+    <row r="7" ht="63.87" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1975,7 +1978,7 @@
       <c r="F7" s="21"/>
       <c r="G7" s="25"/>
     </row>
-    <row r="8" ht="52.21" customHeight="1">
+    <row r="8" ht="63.87" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2009,7 +2012,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52.21" customHeight="1">
+    <row r="9" ht="63.87" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2043,7 +2046,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="52.21" customHeight="1">
+    <row r="10" ht="63.87" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2068,7 +2071,7 @@
       <c r="F10" s="21"/>
       <c r="G10" s="25"/>
     </row>
-    <row r="11" ht="52.21" customHeight="1">
+    <row r="11" ht="63.87" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="28"/>
@@ -2085,7 +2088,7 @@
       <c r="F11" s="21"/>
       <c r="G11" s="28"/>
     </row>
-    <row r="12" ht="52.21" customHeight="1">
+    <row r="12" ht="63.87" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -2120,7 +2123,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52.21" customHeight="1">
+    <row r="13" ht="63.87" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2145,7 +2148,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52.21" customHeight="1">
+    <row r="14" ht="63.87" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -2181,6 +2184,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/쾌지나 칭칭.xlsx
+++ b/sheets/민요/검수/쾌지나 칭칭.xlsx
@@ -1815,11 +1815,11 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
